--- a/보고서_쇼핑검색테스트_중국라벨판매현황.xlsx
+++ b/보고서_쇼핑검색테스트_중국라벨판매현황.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="258">
   <si>
     <t xml:space="preserve">쇼핑검색 광고 입찰가 테스트 현황</t>
   </si>
@@ -3775,83 +3775,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">라벨 마스터 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V14→V15 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">재고 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/21 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">판매현황 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">까지 반영</t>
+      <t xml:space="preserve">재고 프로그램 실재고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10/7) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라벨 마스터 판매현황</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10/6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">까지</t>
     </r>
     <r>
       <rPr>
@@ -3909,36 +3871,46 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">엑셀 재고 기준일</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마스터 시트 제목 “</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">26-09-21 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준”</t>
+    <t xml:space="preserve">실재고 기준일</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재고 프로그램 실재고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -4154,7 +4126,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">현재고 </t>
+      <t xml:space="preserve">실재고 </t>
     </r>
     <r>
       <rPr>
@@ -4173,7 +4145,140 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">엑셀 재고</t>
+      <t xml:space="preserve">재고 프로그램 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체 출고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">총 입고 − 실재고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오픈마켓 판매 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매현황 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일반 판매 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체 출고 − 오픈마켓 판매 </t>
     </r>
     <r>
       <rPr>
@@ -4192,31 +4297,62 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">기준일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) − </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준일 이후 판매</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
+      <t xml:space="preserve">라벨 마스터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 같은 계산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">재질</t>
+  </si>
+  <si>
+    <t xml:space="preserve">규격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">총 입고</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체 출고
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4225,8 +4361,49 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입고−실재고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오픈마켓 판매
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4234,90 +4411,24 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">판매현황에 없는 출고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직접 판매 등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
+        <b val="true"/>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 빠지지 않으니 실제 재고와 함께 확인해 주세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">재질</t>
-  </si>
-  <si>
-    <t xml:space="preserve">규격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">총 입고</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">엑셀 재고
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실재고
 </t>
     </r>
     <r>
@@ -4328,71 +4439,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준일</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준일 이후
-판매</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">현재고</t>
+      <t xml:space="preserve">(10/7)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">상태</t>
@@ -4425,36 +4473,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">주
-판매</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+오픈마켓 판매</t>
     </r>
   </si>
   <si>
@@ -4540,7 +4559,45 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">엑셀 상태</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일반 판매
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출고−오픈마켓</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">비고</t>
@@ -4552,9 +4609,6 @@
     <t xml:space="preserve">35*20</t>
   </si>
   <si>
-    <t xml:space="preserve">판매중</t>
-  </si>
-  <si>
     <t xml:space="preserve">오픈마켓 판매 아님</t>
   </si>
   <si>
@@ -4769,803 +4823,860 @@
     <t xml:space="preserve">70*40</t>
   </si>
   <si>
+    <t xml:space="preserve">80*60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100*60</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지마켓 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쿠팡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">100*70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100*100</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">유포지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30*15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쿠팡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">70*50</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쿠팡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">70*60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100*35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쿠팡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">100*80</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지마켓 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">100*90</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쿠팡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">100*150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">감열지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80*70</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쿠팡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지마켓 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파란 글씨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비고는 라벨 마스터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실재고는 재고 프로그램 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/7). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매현황의 “아트지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80*40” 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/3, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문몰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">롤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 없는 규격이라 어느 규격에도 들어가지 않았습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">규격 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체 출고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오픈마켓 판매</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실재고</t>
+  </si>
+  <si>
     <t xml:space="preserve">품절</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80*60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100*60</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지마켓 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쿠팡 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">100*70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100*100</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">유포지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30*15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쿠팡 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">미판매</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">70*50</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쿠팡 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">70*60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100*35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쿠팡 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">100*80</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지마켓 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">100*90</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쿠팡 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">100*150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">감열지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80*70</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쿠팡 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지마켓 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파란 글씨 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">라벨 마스터 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V14 ‘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마스터’ 시트 값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">판매현황에 있는 “아트지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">80*40” 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9/3, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 마스터에 없는 규격이라 재고 계산에서 빠졌습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">규격 수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엑셀 재고</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이후 판매</t>
   </si>
   <si>
     <t xml:space="preserve">부족</t>
@@ -6224,6 +6335,9 @@
   <si>
     <t xml:space="preserve">메인
 최고 순위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현재고</t>
   </si>
   <si>
     <t xml:space="preserve">판단</t>
@@ -7577,7 +7691,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7726,7 +7840,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7735,6 +7849,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10438,7 +10556,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="29" t="n">
-        <v>46286</v>
+        <v>46302</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>118</v>
@@ -10525,7 +10643,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="32" t="n">
         <f aca="false">F53</f>
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="22" t="str">
@@ -10697,15 +10815,15 @@
       <c r="C23" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="D23" s="27" t="n">
-        <v>104</v>
+      <c r="D23" s="36" t="n">
+        <f aca="false">C23-F23</f>
+        <v>16</v>
       </c>
       <c r="E23" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A23,원본_판매현황!$C$2:$C$500,$B23,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A23,원본_판매현황!$C$2:$C$500,$B23,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
         <v>0</v>
       </c>
       <c r="F23" s="37" t="n">
-        <f aca="false">D23-E23</f>
         <v>104</v>
       </c>
       <c r="G23" s="38" t="str">
@@ -10723,11 +10841,12 @@
       <c r="J23" s="27" t="n">
         <v>2750</v>
       </c>
-      <c r="K23" s="23" t="s">
+      <c r="K23" s="36" t="n">
+        <f aca="false">D23-E23</f>
+        <v>16</v>
+      </c>
+      <c r="L23" s="23" t="s">
         <v>150</v>
-      </c>
-      <c r="L23" s="23" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10735,20 +10854,20 @@
         <v>148</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="D24" s="27" t="n">
-        <v>41</v>
+      <c r="D24" s="36" t="n">
+        <f aca="false">C24-F24</f>
+        <v>71</v>
       </c>
       <c r="E24" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A24,원본_판매현황!$C$2:$C$500,$B24,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>12</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A24,원본_판매현황!$C$2:$C$500,$B24,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>14</v>
       </c>
       <c r="F24" s="37" t="n">
-        <f aca="false">D24-E24</f>
         <v>29</v>
       </c>
       <c r="G24" s="38" t="str">
@@ -10766,11 +10885,12 @@
       <c r="J24" s="27" t="n">
         <v>2750</v>
       </c>
-      <c r="K24" s="23" t="s">
-        <v>150</v>
+      <c r="K24" s="36" t="n">
+        <f aca="false">D24-E24</f>
+        <v>57</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10778,20 +10898,20 @@
         <v>148</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="D25" s="27" t="n">
-        <v>42</v>
+      <c r="D25" s="36" t="n">
+        <f aca="false">C25-F25</f>
+        <v>78</v>
       </c>
       <c r="E25" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A25,원본_판매현황!$C$2:$C$500,$B25,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A25,원본_판매현황!$C$2:$C$500,$B25,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
         <v>0</v>
       </c>
       <c r="F25" s="37" t="n">
-        <f aca="false">D25-E25</f>
         <v>42</v>
       </c>
       <c r="G25" s="38" t="str">
@@ -10809,11 +10929,12 @@
       <c r="J25" s="27" t="n">
         <v>4400</v>
       </c>
-      <c r="K25" s="23" t="s">
-        <v>150</v>
+      <c r="K25" s="36" t="n">
+        <f aca="false">D25-E25</f>
+        <v>78</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10821,20 +10942,20 @@
         <v>148</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C26" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="D26" s="27" t="n">
-        <v>18</v>
+      <c r="D26" s="36" t="n">
+        <f aca="false">C26-F26</f>
+        <v>52</v>
       </c>
       <c r="E26" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A26,원본_판매현황!$C$2:$C$500,$B26,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A26,원본_판매현황!$C$2:$C$500,$B26,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>22</v>
       </c>
       <c r="F26" s="37" t="n">
-        <f aca="false">D26-E26</f>
         <v>18</v>
       </c>
       <c r="G26" s="38" t="str">
@@ -10852,11 +10973,12 @@
       <c r="J26" s="27" t="n">
         <v>3850</v>
       </c>
-      <c r="K26" s="23" t="s">
-        <v>150</v>
+      <c r="K26" s="36" t="n">
+        <f aca="false">D26-E26</f>
+        <v>30</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10864,21 +10986,21 @@
         <v>148</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C27" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="D27" s="27" t="n">
-        <v>98</v>
+      <c r="D27" s="36" t="n">
+        <f aca="false">C27-F27</f>
+        <v>9</v>
       </c>
       <c r="E27" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A27,원본_판매현황!$C$2:$C$500,$B27,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>2</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A27,원본_판매현황!$C$2:$C$500,$B27,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>9</v>
       </c>
       <c r="F27" s="37" t="n">
-        <f aca="false">D27-E27</f>
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G27" s="38" t="str">
         <f aca="false">IF(F27&lt;=0,"품절",IF(F27&lt;=$C$10,"부족","여유"))</f>
@@ -10890,16 +11012,17 @@
       </c>
       <c r="I27" s="39" t="n">
         <f aca="false">IF(OR(H27=0,F27&lt;=0),"-",F27/(H27/4))</f>
-        <v>48</v>
+        <v>45.5</v>
       </c>
       <c r="J27" s="27" t="n">
         <v>4930</v>
       </c>
-      <c r="K27" s="23" t="s">
-        <v>150</v>
+      <c r="K27" s="36" t="n">
+        <f aca="false">D27-E27</f>
+        <v>0</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10907,20 +11030,20 @@
         <v>148</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C28" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="D28" s="27" t="n">
+      <c r="D28" s="36" t="n">
+        <f aca="false">C28-F28</f>
+        <v>50</v>
+      </c>
+      <c r="E28" s="36" t="n">
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A28,원본_판매현황!$C$2:$C$500,$B28,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A28,원본_판매현황!$C$2:$C$500,$B28,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
-      </c>
       <c r="F28" s="37" t="n">
-        <f aca="false">D28-E28</f>
         <v>0</v>
       </c>
       <c r="G28" s="38" t="str">
@@ -10936,8 +11059,9 @@
         <v>-</v>
       </c>
       <c r="J28" s="27"/>
-      <c r="K28" s="23" t="s">
-        <v>161</v>
+      <c r="K28" s="36" t="n">
+        <f aca="false">D28-E28</f>
+        <v>50</v>
       </c>
       <c r="L28" s="23"/>
     </row>
@@ -10946,20 +11070,20 @@
         <v>148</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C29" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="D29" s="27" t="n">
-        <v>14</v>
+      <c r="D29" s="36" t="n">
+        <f aca="false">C29-F29</f>
+        <v>87</v>
       </c>
       <c r="E29" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A29,원본_판매현황!$C$2:$C$500,$B29,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>1</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A29,원본_판매현황!$C$2:$C$500,$B29,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>2</v>
       </c>
       <c r="F29" s="37" t="n">
-        <f aca="false">D29-E29</f>
         <v>13</v>
       </c>
       <c r="G29" s="38" t="str">
@@ -10977,11 +11101,12 @@
       <c r="J29" s="27" t="n">
         <v>7150</v>
       </c>
-      <c r="K29" s="23" t="s">
+      <c r="K29" s="36" t="n">
+        <f aca="false">D29-E29</f>
+        <v>85</v>
+      </c>
+      <c r="L29" s="23" t="s">
         <v>150</v>
-      </c>
-      <c r="L29" s="23" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10989,20 +11114,20 @@
         <v>148</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C30" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="D30" s="27" t="n">
-        <v>8</v>
+      <c r="D30" s="36" t="n">
+        <f aca="false">C30-F30</f>
+        <v>72</v>
       </c>
       <c r="E30" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A30,원본_판매현황!$C$2:$C$500,$B30,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A30,원본_판매현황!$C$2:$C$500,$B30,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>13</v>
       </c>
       <c r="F30" s="37" t="n">
-        <f aca="false">D30-E30</f>
         <v>8</v>
       </c>
       <c r="G30" s="38" t="str">
@@ -11020,11 +11145,12 @@
       <c r="J30" s="27" t="n">
         <v>7150</v>
       </c>
-      <c r="K30" s="23" t="s">
-        <v>150</v>
+      <c r="K30" s="36" t="n">
+        <f aca="false">D30-E30</f>
+        <v>59</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11032,20 +11158,20 @@
         <v>148</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C31" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="D31" s="27" t="n">
-        <v>2</v>
+      <c r="D31" s="36" t="n">
+        <f aca="false">C31-F31</f>
+        <v>68</v>
       </c>
       <c r="E31" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A31,원본_판매현황!$C$2:$C$500,$B31,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A31,원본_판매현황!$C$2:$C$500,$B31,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
         <v>0</v>
       </c>
       <c r="F31" s="37" t="n">
-        <f aca="false">D31-E31</f>
         <v>2</v>
       </c>
       <c r="G31" s="38" t="str">
@@ -11063,11 +11189,12 @@
       <c r="J31" s="27" t="n">
         <v>10760</v>
       </c>
-      <c r="K31" s="23" t="s">
+      <c r="K31" s="36" t="n">
+        <f aca="false">D31-E31</f>
+        <v>68</v>
+      </c>
+      <c r="L31" s="23" t="s">
         <v>150</v>
-      </c>
-      <c r="L31" s="23" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11075,20 +11202,20 @@
         <v>148</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C32" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="D32" s="27" t="n">
-        <v>30</v>
+      <c r="D32" s="36" t="n">
+        <f aca="false">C32-F32</f>
+        <v>50</v>
       </c>
       <c r="E32" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A32,원본_판매현황!$C$2:$C$500,$B32,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A32,원본_판매현황!$C$2:$C$500,$B32,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>11</v>
       </c>
       <c r="F32" s="37" t="n">
-        <f aca="false">D32-E32</f>
         <v>30</v>
       </c>
       <c r="G32" s="38" t="str">
@@ -11106,32 +11233,33 @@
       <c r="J32" s="27" t="n">
         <v>7700</v>
       </c>
-      <c r="K32" s="23" t="s">
-        <v>150</v>
+      <c r="K32" s="36" t="n">
+        <f aca="false">D32-E32</f>
+        <v>39</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C33" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="D33" s="27" t="n">
-        <v>70</v>
+      <c r="D33" s="36" t="n">
+        <f aca="false">C33-F33</f>
+        <v>12</v>
       </c>
       <c r="E33" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A33,원본_판매현황!$C$2:$C$500,$B33,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>2</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A33,원본_판매현황!$C$2:$C$500,$B33,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>12</v>
       </c>
       <c r="F33" s="37" t="n">
-        <f aca="false">D33-E33</f>
         <v>68</v>
       </c>
       <c r="G33" s="38" t="str">
@@ -11149,32 +11277,33 @@
       <c r="J33" s="27" t="n">
         <v>5020</v>
       </c>
-      <c r="K33" s="23" t="s">
-        <v>150</v>
+      <c r="K33" s="36" t="n">
+        <f aca="false">D33-E33</f>
+        <v>0</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="D34" s="27" t="n">
-        <v>80</v>
+      <c r="D34" s="36" t="n">
+        <f aca="false">C34-F34</f>
+        <v>0</v>
       </c>
       <c r="E34" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A34,원본_판매현황!$C$2:$C$500,$B34,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A34,원본_판매현황!$C$2:$C$500,$B34,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
         <v>0</v>
       </c>
       <c r="F34" s="37" t="n">
-        <f aca="false">D34-E34</f>
         <v>80</v>
       </c>
       <c r="G34" s="38" t="str">
@@ -11192,30 +11321,31 @@
       <c r="J34" s="27" t="n">
         <v>6140</v>
       </c>
-      <c r="K34" s="23" t="s">
-        <v>171</v>
+      <c r="K34" s="36" t="n">
+        <f aca="false">D34-E34</f>
+        <v>0</v>
       </c>
       <c r="L34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C35" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="D35" s="27" t="n">
-        <v>0</v>
+      <c r="D35" s="36" t="n">
+        <f aca="false">C35-F35</f>
+        <v>50</v>
       </c>
       <c r="E35" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A35,원본_판매현황!$C$2:$C$500,$B35,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A35,원본_판매현황!$C$2:$C$500,$B35,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>50</v>
       </c>
       <c r="F35" s="37" t="n">
-        <f aca="false">D35-E35</f>
         <v>0</v>
       </c>
       <c r="G35" s="38" t="str">
@@ -11231,32 +11361,33 @@
         <v>-</v>
       </c>
       <c r="J35" s="27"/>
-      <c r="K35" s="23" t="s">
-        <v>161</v>
+      <c r="K35" s="36" t="n">
+        <f aca="false">D35-E35</f>
+        <v>0</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C36" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="D36" s="27" t="n">
-        <v>2</v>
+      <c r="D36" s="36" t="n">
+        <f aca="false">C36-F36</f>
+        <v>48</v>
       </c>
       <c r="E36" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A36,원본_판매현황!$C$2:$C$500,$B36,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A36,원본_판매현황!$C$2:$C$500,$B36,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>5</v>
       </c>
       <c r="F36" s="37" t="n">
-        <f aca="false">D36-E36</f>
         <v>2</v>
       </c>
       <c r="G36" s="38" t="str">
@@ -11274,32 +11405,33 @@
       <c r="J36" s="27" t="n">
         <v>5780</v>
       </c>
-      <c r="K36" s="23" t="s">
-        <v>150</v>
+      <c r="K36" s="36" t="n">
+        <f aca="false">D36-E36</f>
+        <v>43</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C37" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="D37" s="27" t="n">
-        <v>20</v>
+      <c r="D37" s="36" t="n">
+        <f aca="false">C37-F37</f>
+        <v>45</v>
       </c>
       <c r="E37" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A37,원본_판매현황!$C$2:$C$500,$B37,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>5</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A37,원본_판매현황!$C$2:$C$500,$B37,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>12</v>
       </c>
       <c r="F37" s="37" t="n">
-        <f aca="false">D37-E37</f>
         <v>15</v>
       </c>
       <c r="G37" s="38" t="str">
@@ -11317,32 +11449,33 @@
       <c r="J37" s="27" t="n">
         <v>5980</v>
       </c>
-      <c r="K37" s="23" t="s">
-        <v>150</v>
+      <c r="K37" s="36" t="n">
+        <f aca="false">D37-E37</f>
+        <v>33</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C38" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="D38" s="27" t="n">
-        <v>50</v>
+      <c r="D38" s="36" t="n">
+        <f aca="false">C38-F38</f>
+        <v>0</v>
       </c>
       <c r="E38" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A38,원본_판매현황!$C$2:$C$500,$B38,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A38,원본_판매현황!$C$2:$C$500,$B38,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
         <v>0</v>
       </c>
       <c r="F38" s="37" t="n">
-        <f aca="false">D38-E38</f>
         <v>50</v>
       </c>
       <c r="G38" s="38" t="str">
@@ -11360,30 +11493,31 @@
       <c r="J38" s="27" t="n">
         <v>7170</v>
       </c>
-      <c r="K38" s="23" t="s">
-        <v>171</v>
+      <c r="K38" s="36" t="n">
+        <f aca="false">D38-E38</f>
+        <v>0</v>
       </c>
       <c r="L38" s="23"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C39" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="D39" s="27" t="n">
-        <v>36</v>
+      <c r="D39" s="36" t="n">
+        <f aca="false">C39-F39</f>
+        <v>14</v>
       </c>
       <c r="E39" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A39,원본_판매현황!$C$2:$C$500,$B39,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A39,원본_판매현황!$C$2:$C$500,$B39,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>1</v>
       </c>
       <c r="F39" s="37" t="n">
-        <f aca="false">D39-E39</f>
         <v>36</v>
       </c>
       <c r="G39" s="38" t="str">
@@ -11401,32 +11535,33 @@
       <c r="J39" s="27" t="n">
         <v>14180</v>
       </c>
-      <c r="K39" s="23" t="s">
-        <v>150</v>
+      <c r="K39" s="36" t="n">
+        <f aca="false">D39-E39</f>
+        <v>13</v>
       </c>
       <c r="L39" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C40" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="D40" s="27" t="n">
-        <v>0</v>
+      <c r="D40" s="36" t="n">
+        <f aca="false">C40-F40</f>
+        <v>55</v>
       </c>
       <c r="E40" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A40,원본_판매현황!$C$2:$C$500,$B40,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A40,원본_판매현황!$C$2:$C$500,$B40,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>2</v>
       </c>
       <c r="F40" s="37" t="n">
-        <f aca="false">D40-E40</f>
         <v>0</v>
       </c>
       <c r="G40" s="38" t="str">
@@ -11444,32 +11579,33 @@
       <c r="J40" s="27" t="n">
         <v>10590</v>
       </c>
-      <c r="K40" s="23" t="s">
-        <v>161</v>
+      <c r="K40" s="36" t="n">
+        <f aca="false">D40-E40</f>
+        <v>53</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C41" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="D41" s="27" t="n">
-        <v>8</v>
+      <c r="D41" s="36" t="n">
+        <f aca="false">C41-F41</f>
+        <v>42</v>
       </c>
       <c r="E41" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A41,원본_판매현황!$C$2:$C$500,$B41,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A41,원본_판매현황!$C$2:$C$500,$B41,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>19</v>
       </c>
       <c r="F41" s="37" t="n">
-        <f aca="false">D41-E41</f>
         <v>8</v>
       </c>
       <c r="G41" s="38" t="str">
@@ -11487,32 +11623,33 @@
       <c r="J41" s="27" t="n">
         <v>8920</v>
       </c>
-      <c r="K41" s="23" t="s">
-        <v>150</v>
+      <c r="K41" s="36" t="n">
+        <f aca="false">D41-E41</f>
+        <v>23</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C42" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="D42" s="27" t="n">
-        <v>27</v>
+      <c r="D42" s="36" t="n">
+        <f aca="false">C42-F42</f>
+        <v>23</v>
       </c>
       <c r="E42" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A42,원본_판매현황!$C$2:$C$500,$B42,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A42,원본_판매현황!$C$2:$C$500,$B42,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>3</v>
       </c>
       <c r="F42" s="37" t="n">
-        <f aca="false">D42-E42</f>
         <v>27</v>
       </c>
       <c r="G42" s="38" t="str">
@@ -11530,32 +11667,33 @@
       <c r="J42" s="27" t="n">
         <v>13930</v>
       </c>
-      <c r="K42" s="23" t="s">
-        <v>150</v>
+      <c r="K42" s="36" t="n">
+        <f aca="false">D42-E42</f>
+        <v>20</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C43" s="27" t="n">
         <v>67</v>
       </c>
-      <c r="D43" s="27" t="n">
-        <v>0</v>
+      <c r="D43" s="36" t="n">
+        <f aca="false">C43-F43</f>
+        <v>67</v>
       </c>
       <c r="E43" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A43,원본_판매현황!$C$2:$C$500,$B43,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A43,원본_판매현황!$C$2:$C$500,$B43,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>14</v>
       </c>
       <c r="F43" s="37" t="n">
-        <f aca="false">D43-E43</f>
         <v>0</v>
       </c>
       <c r="G43" s="38" t="str">
@@ -11573,32 +11711,33 @@
       <c r="J43" s="27" t="n">
         <v>8490</v>
       </c>
-      <c r="K43" s="23" t="s">
-        <v>161</v>
+      <c r="K43" s="36" t="n">
+        <f aca="false">D43-E43</f>
+        <v>53</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C44" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="D44" s="27" t="n">
-        <v>2</v>
+      <c r="D44" s="36" t="n">
+        <f aca="false">C44-F44</f>
+        <v>48</v>
       </c>
       <c r="E44" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A44,원본_판매현황!$C$2:$C$500,$B44,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A44,원본_판매현황!$C$2:$C$500,$B44,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>5</v>
       </c>
       <c r="F44" s="37" t="n">
-        <f aca="false">D44-E44</f>
         <v>2</v>
       </c>
       <c r="G44" s="38" t="str">
@@ -11616,33 +11755,34 @@
       <c r="J44" s="27" t="n">
         <v>10200</v>
       </c>
-      <c r="K44" s="23" t="s">
-        <v>150</v>
+      <c r="K44" s="36" t="n">
+        <f aca="false">D44-E44</f>
+        <v>43</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C45" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="D45" s="27" t="n">
-        <v>53</v>
+      <c r="D45" s="36" t="n">
+        <f aca="false">C45-F45</f>
+        <v>16</v>
       </c>
       <c r="E45" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A45,원본_판매현황!$C$2:$C$500,$B45,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>10</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A45,원본_판매현황!$C$2:$C$500,$B45,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>11</v>
       </c>
       <c r="F45" s="37" t="n">
-        <f aca="false">D45-E45</f>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G45" s="38" t="str">
         <f aca="false">IF(F45&lt;=0,"품절",IF(F45&lt;=$C$10,"부족","여유"))</f>
@@ -11654,37 +11794,38 @@
       </c>
       <c r="I45" s="39" t="n">
         <f aca="false">IF(OR(H45=0,F45&lt;=0),"-",F45/(H45/4))</f>
-        <v>17.2</v>
+        <v>16</v>
       </c>
       <c r="J45" s="27" t="n">
         <v>5590</v>
       </c>
-      <c r="K45" s="23" t="s">
-        <v>150</v>
+      <c r="K45" s="36" t="n">
+        <f aca="false">D45-E45</f>
+        <v>5</v>
       </c>
       <c r="L45" s="23" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C46" s="27" t="n">
         <v>360</v>
       </c>
-      <c r="D46" s="27" t="n">
-        <v>336</v>
+      <c r="D46" s="36" t="n">
+        <f aca="false">C46-F46</f>
+        <v>31</v>
       </c>
       <c r="E46" s="36" t="n">
-        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A46,원본_판매현황!$C$2:$C$500,$B46,원본_판매현황!$A$2:$A$500,"&gt;"&amp;$C$5,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>7</v>
+        <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A46,원본_판매현황!$C$2:$C$500,$B46,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
+        <v>23</v>
       </c>
       <c r="F46" s="37" t="n">
-        <f aca="false">D46-E46</f>
         <v>329</v>
       </c>
       <c r="G46" s="38" t="str">
@@ -11702,16 +11843,17 @@
       <c r="J46" s="27" t="n">
         <v>7550</v>
       </c>
-      <c r="K46" s="23" t="s">
-        <v>150</v>
+      <c r="K46" s="36" t="n">
+        <f aca="false">D46-E46</f>
+        <v>8</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11719,28 +11861,28 @@
         <v>136</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>138</v>
       </c>
       <c r="D49" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H49" s="10" t="s">
+      <c r="I49" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11757,15 +11899,15 @@
       </c>
       <c r="D50" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A50,$D$23:$D$46)</f>
-        <v>357</v>
+        <v>553</v>
       </c>
       <c r="E50" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A50,$E$23:$E$46)</f>
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="F50" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A50,$F$23:$F$46)</f>
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G50" s="36" t="n">
         <f aca="false">COUNTIFS($A$23:$A$46,$A50,$G$23:$G$46,"품절")</f>
@@ -11782,7 +11924,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B51" s="36" t="n">
         <f aca="false">COUNTIF($A$23:$A$46,$A51)</f>
@@ -11794,11 +11936,11 @@
       </c>
       <c r="D51" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A51,$D$23:$D$46)</f>
-        <v>295</v>
+        <v>404</v>
       </c>
       <c r="E51" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A51,$E$23:$E$46)</f>
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="F51" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A51,$F$23:$F$46)</f>
@@ -11819,7 +11961,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B52" s="36" t="n">
         <f aca="false">COUNTIF($A$23:$A$46,$A52)</f>
@@ -11831,15 +11973,15 @@
       </c>
       <c r="D52" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A52,$D$23:$D$46)</f>
-        <v>389</v>
+        <v>47</v>
       </c>
       <c r="E52" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A52,$E$23:$E$46)</f>
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F52" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A52,$F$23:$F$46)</f>
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G52" s="36" t="n">
         <f aca="false">COUNTIFS($A$23:$A$46,$A52,$G$23:$G$46,"품절")</f>
@@ -11858,42 +12000,42 @@
       <c r="A53" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="37" t="n">
+      <c r="B53" s="40" t="n">
         <f aca="false">SUM(B50:B52)</f>
         <v>24</v>
       </c>
-      <c r="C53" s="37" t="n">
+      <c r="C53" s="40" t="n">
         <f aca="false">SUM(C50:C52)</f>
         <v>1998</v>
       </c>
-      <c r="D53" s="37" t="n">
+      <c r="D53" s="40" t="n">
         <f aca="false">SUM(D50:D52)</f>
-        <v>1041</v>
-      </c>
-      <c r="E53" s="37" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E53" s="40" t="n">
         <f aca="false">SUM(E50:E52)</f>
-        <v>39</v>
-      </c>
-      <c r="F53" s="37" t="n">
+        <v>228</v>
+      </c>
+      <c r="F53" s="40" t="n">
         <f aca="false">SUM(F50:F52)</f>
-        <v>1002</v>
-      </c>
-      <c r="G53" s="37" t="n">
+        <v>994</v>
+      </c>
+      <c r="G53" s="40" t="n">
         <f aca="false">SUM(G50:G52)</f>
         <v>4</v>
       </c>
-      <c r="H53" s="37" t="n">
+      <c r="H53" s="40" t="n">
         <f aca="false">SUM(H50:H52)</f>
         <v>5</v>
       </c>
-      <c r="I53" s="37" t="n">
+      <c r="I53" s="40" t="n">
         <f aca="false">SUM(I50:I52)</f>
         <v>48</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -11909,101 +12051,101 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B57" s="3"/>
-      <c r="C57" s="40" t="n">
+      <c r="C57" s="41" t="n">
         <f aca="false">$C$7-($C$8-$C$7+1)</f>
         <v>46284</v>
       </c>
-      <c r="D57" s="40" t="n">
+      <c r="D57" s="41" t="n">
         <f aca="false">$C$7-1</f>
         <v>46292</v>
       </c>
-      <c r="E57" s="41" t="n">
+      <c r="E57" s="42" t="n">
         <f aca="false">D57-C57+1</f>
         <v>9</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B58" s="3"/>
-      <c r="C58" s="40" t="n">
+      <c r="C58" s="41" t="n">
         <f aca="false">$C$7</f>
         <v>46293</v>
       </c>
-      <c r="D58" s="40" t="n">
+      <c r="D58" s="41" t="n">
         <f aca="false">$C$8</f>
         <v>46301</v>
       </c>
-      <c r="E58" s="41" t="n">
+      <c r="E58" s="42" t="n">
         <f aca="false">D58-C58+1</f>
         <v>9</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="29" t="n">
         <v>46235</v>
       </c>
-      <c r="D59" s="40" t="n">
+      <c r="D59" s="41" t="n">
         <f aca="false">$C$7-1</f>
         <v>46292</v>
       </c>
-      <c r="E59" s="41" t="n">
+      <c r="E59" s="42" t="n">
         <f aca="false">D59-C59+1</f>
         <v>58</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D61" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="E61" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="F61" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="G61" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="H61" s="10" t="s">
+      <c r="I61" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="I61" s="10" t="s">
+      <c r="J61" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J61" s="10" t="s">
+      <c r="K61" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="K61" s="10" t="s">
+      <c r="L61" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="L61" s="10" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B62" s="11"/>
       <c r="C62" s="36" t="n">
@@ -12014,19 +12156,19 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰")</f>
         <v>5</v>
       </c>
-      <c r="E62" s="37" t="n">
+      <c r="E62" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰")</f>
         <v>4</v>
       </c>
-      <c r="F62" s="37" t="n">
+      <c r="F62" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰")</f>
         <v>8</v>
       </c>
-      <c r="G62" s="42" t="n">
+      <c r="G62" s="43" t="n">
         <f aca="false">E62-C62</f>
         <v>3</v>
       </c>
-      <c r="H62" s="42" t="n">
+      <c r="H62" s="43" t="n">
         <f aca="false">F62-D62</f>
         <v>3</v>
       </c>
@@ -12038,18 +12180,18 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"전문몰")/$E$59*$E$58</f>
         <v>6.36206896551724</v>
       </c>
-      <c r="K62" s="43" t="n">
+      <c r="K62" s="44" t="n">
         <f aca="false">IF(I62=0,"-",E62/I62-1)</f>
         <v>0.432098765432099</v>
       </c>
-      <c r="L62" s="43" t="n">
+      <c r="L62" s="44" t="n">
         <f aca="false">IF(J62=0,"-",F62/J62-1)</f>
         <v>0.257452574525745</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B63" s="22"/>
       <c r="C63" s="36" t="n">
@@ -12060,19 +12202,19 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"&lt;&gt;전문몰")</f>
         <v>0</v>
       </c>
-      <c r="E63" s="37" t="n">
+      <c r="E63" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"&lt;&gt;전문몰")</f>
         <v>6</v>
       </c>
-      <c r="F63" s="37" t="n">
+      <c r="F63" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"&lt;&gt;전문몰")</f>
         <v>31</v>
       </c>
-      <c r="G63" s="42" t="n">
+      <c r="G63" s="43" t="n">
         <f aca="false">E63-C63</f>
         <v>6</v>
       </c>
-      <c r="H63" s="42" t="n">
+      <c r="H63" s="43" t="n">
         <f aca="false">F63-D63</f>
         <v>31</v>
       </c>
@@ -12084,18 +12226,18 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"&lt;&gt;전문몰")/$E$59*$E$58</f>
         <v>7.75862068965517</v>
       </c>
-      <c r="K63" s="43" t="n">
+      <c r="K63" s="44" t="n">
         <f aca="false">IF(I63=0,"-",E63/I63-1)</f>
         <v>2.51515151515152</v>
       </c>
-      <c r="L63" s="43" t="n">
+      <c r="L63" s="44" t="n">
         <f aca="false">IF(J63=0,"-",F63/J63-1)</f>
         <v>2.99555555555556</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B64" s="11"/>
       <c r="C64" s="36" t="n">
@@ -12106,19 +12248,19 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57)</f>
         <v>5</v>
       </c>
-      <c r="E64" s="37" t="n">
+      <c r="E64" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8)</f>
         <v>10</v>
       </c>
-      <c r="F64" s="37" t="n">
+      <c r="F64" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8)</f>
         <v>39</v>
       </c>
-      <c r="G64" s="42" t="n">
+      <c r="G64" s="43" t="n">
         <f aca="false">E64-C64</f>
         <v>9</v>
       </c>
-      <c r="H64" s="42" t="n">
+      <c r="H64" s="43" t="n">
         <f aca="false">F64-D64</f>
         <v>34</v>
       </c>
@@ -12130,18 +12272,18 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59)/$E$59*$E$58</f>
         <v>14.1206896551724</v>
       </c>
-      <c r="K64" s="43" t="n">
+      <c r="K64" s="44" t="n">
         <f aca="false">IF(I64=0,"-",E64/I64-1)</f>
         <v>1.22222222222222</v>
       </c>
-      <c r="L64" s="43" t="n">
+      <c r="L64" s="44" t="n">
         <f aca="false">IF(J64=0,"-",F64/J64-1)</f>
         <v>1.76190476190476</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B65" s="22"/>
       <c r="C65" s="36" t="n">
@@ -12152,19 +12294,19 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"아트지")</f>
         <v>5</v>
       </c>
-      <c r="E65" s="37" t="n">
+      <c r="E65" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"아트지")</f>
         <v>1</v>
       </c>
-      <c r="F65" s="37" t="n">
+      <c r="F65" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"아트지")</f>
         <v>1</v>
       </c>
-      <c r="G65" s="42" t="n">
+      <c r="G65" s="43" t="n">
         <f aca="false">E65-C65</f>
         <v>0</v>
       </c>
-      <c r="H65" s="42" t="n">
+      <c r="H65" s="43" t="n">
         <f aca="false">F65-D65</f>
         <v>-4</v>
       </c>
@@ -12176,18 +12318,18 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"아트지")/$E$59*$E$58</f>
         <v>2.48275862068966</v>
       </c>
-      <c r="K65" s="43" t="n">
+      <c r="K65" s="44" t="n">
         <f aca="false">IF(I65=0,"-",E65/I65-1)</f>
         <v>-0.0793650793650794</v>
       </c>
-      <c r="L65" s="43" t="n">
+      <c r="L65" s="44" t="n">
         <f aca="false">IF(J65=0,"-",F65/J65-1)</f>
         <v>-0.597222222222222</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B66" s="22"/>
       <c r="C66" s="36" t="n">
@@ -12198,19 +12340,19 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"유포지")</f>
         <v>0</v>
       </c>
-      <c r="E66" s="37" t="n">
+      <c r="E66" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"유포지")</f>
         <v>3</v>
       </c>
-      <c r="F66" s="37" t="n">
+      <c r="F66" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"유포지")</f>
         <v>7</v>
       </c>
-      <c r="G66" s="42" t="n">
+      <c r="G66" s="43" t="n">
         <f aca="false">E66-C66</f>
         <v>3</v>
       </c>
-      <c r="H66" s="42" t="n">
+      <c r="H66" s="43" t="n">
         <f aca="false">F66-D66</f>
         <v>7</v>
       </c>
@@ -12222,18 +12364,18 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"유포지")/$E$59*$E$58</f>
         <v>3.87931034482759</v>
       </c>
-      <c r="K66" s="43" t="n">
+      <c r="K66" s="44" t="n">
         <f aca="false">IF(I66=0,"-",E66/I66-1)</f>
         <v>0.757575757575758</v>
       </c>
-      <c r="L66" s="43" t="n">
+      <c r="L66" s="44" t="n">
         <f aca="false">IF(J66=0,"-",F66/J66-1)</f>
         <v>0.804444444444445</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B67" s="22"/>
       <c r="C67" s="36" t="n">
@@ -12244,19 +12386,19 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"감열지")</f>
         <v>0</v>
       </c>
-      <c r="E67" s="37" t="n">
+      <c r="E67" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"감열지")</f>
         <v>0</v>
       </c>
-      <c r="F67" s="37" t="n">
+      <c r="F67" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"감열지")</f>
         <v>0</v>
       </c>
-      <c r="G67" s="42" t="n">
+      <c r="G67" s="43" t="n">
         <f aca="false">E67-C67</f>
         <v>0</v>
       </c>
-      <c r="H67" s="42" t="n">
+      <c r="H67" s="43" t="n">
         <f aca="false">F67-D67</f>
         <v>0</v>
       </c>
@@ -12268,23 +12410,23 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"감열지")/$E$59*$E$58</f>
         <v>0</v>
       </c>
-      <c r="K67" s="43" t="str">
+      <c r="K67" s="44" t="str">
         <f aca="false">IF(I67=0,"-",E67/I67-1)</f>
         <v>-</v>
       </c>
-      <c r="L67" s="43" t="str">
+      <c r="L67" s="44" t="str">
         <f aca="false">IF(J67=0,"-",F67/J67-1)</f>
         <v>-</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="44" t="s">
-        <v>217</v>
+      <c r="A69" s="45" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>136</v>
@@ -12293,88 +12435,88 @@
         <v>137</v>
       </c>
       <c r="D70" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E70" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="E70" s="10" t="s">
-        <v>220</v>
-      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="45" t="n">
+      <c r="A71" s="46" t="n">
         <v>46295</v>
       </c>
-      <c r="B71" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="C71" s="47" t="s">
-        <v>174</v>
-      </c>
-      <c r="D71" s="46" t="s">
+      <c r="B71" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="D71" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E71" s="48" t="n">
+      <c r="E71" s="49" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="45" t="n">
+      <c r="A72" s="46" t="n">
         <v>46295</v>
       </c>
-      <c r="B72" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="C72" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="D72" s="46" t="s">
+      <c r="B72" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C72" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="D72" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E72" s="48" t="n">
+      <c r="E72" s="49" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="45" t="n">
+      <c r="A73" s="46" t="n">
         <v>46295</v>
       </c>
-      <c r="B73" s="46" t="s">
+      <c r="B73" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="C73" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="D73" s="46" t="s">
+      <c r="C73" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="D73" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E73" s="48" t="n">
+      <c r="E73" s="49" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="45" t="n">
+      <c r="A74" s="46" t="n">
         <v>46297</v>
       </c>
-      <c r="B74" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="C74" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="D74" s="46" t="s">
+      <c r="B74" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="D74" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E74" s="48" t="n">
+      <c r="E74" s="49" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="45" t="s">
         <v>221</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="44" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12388,28 +12530,28 @@
         <v>137</v>
       </c>
       <c r="D78" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E78" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="F78" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F78" s="10" t="s">
+      <c r="G78" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="G78" s="10" t="s">
+      <c r="H78" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="H78" s="10" t="s">
+      <c r="I78" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="I78" s="10" t="s">
+      <c r="J78" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="J78" s="10" t="s">
+      <c r="K78" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="K78" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="L78" s="10" t="s">
         <v>230</v>
@@ -12420,10 +12562,10 @@
         <v>31</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="C79" s="49" t="s">
-        <v>169</v>
+        <v>166</v>
+      </c>
+      <c r="C79" s="50" t="s">
+        <v>167</v>
       </c>
       <c r="D79" s="36" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B79,원본_판매현황!$C$2:$C$500,$C79)</f>
@@ -12433,11 +12575,11 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B79,원본_판매현황!$C$2:$C$500,$C79)</f>
         <v>0</v>
       </c>
-      <c r="F79" s="37" t="n">
+      <c r="F79" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B79,원본_판매현황!$C$2:$C$500,$C79)</f>
         <v>2</v>
       </c>
-      <c r="G79" s="37" t="n">
+      <c r="G79" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B79,원본_판매현황!$C$2:$C$500,$C79)</f>
         <v>2</v>
       </c>
@@ -12449,7 +12591,7 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$B$2:$B$500,$B79,원본_판매현황!$C$2:$C$500,$C79)</f>
         <v>2</v>
       </c>
-      <c r="J79" s="50" t="str">
+      <c r="J79" s="51" t="str">
         <f aca="false">'1.쇼핑검색 테스트'!I19</f>
         <v>1위</v>
       </c>
@@ -12457,7 +12599,7 @@
         <f aca="false">F33</f>
         <v>68</v>
       </c>
-      <c r="L79" s="51" t="str">
+      <c r="L79" s="52" t="str">
         <f aca="false">IF(F79&gt;D79,"광고 중 전문몰 판매 늘어남",IF(F79=0,"광고 중 전문몰 판매 없음","변화 없음"))</f>
         <v>광고 중 전문몰 판매 늘어남</v>
       </c>
@@ -12467,10 +12609,10 @@
         <v>34</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="C80" s="49" t="s">
-        <v>166</v>
+        <v>182</v>
+      </c>
+      <c r="C80" s="50" t="s">
+        <v>164</v>
       </c>
       <c r="D80" s="36" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B80,원본_판매현황!$C$2:$C$500,$C80)</f>
@@ -12480,11 +12622,11 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B80,원본_판매현황!$C$2:$C$500,$C80)</f>
         <v>0</v>
       </c>
-      <c r="F80" s="37" t="n">
+      <c r="F80" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B80,원본_판매현황!$C$2:$C$500,$C80)</f>
         <v>0</v>
       </c>
-      <c r="G80" s="37" t="n">
+      <c r="G80" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B80,원본_판매현황!$C$2:$C$500,$C80)</f>
         <v>0</v>
       </c>
@@ -12496,7 +12638,7 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$B$2:$B$500,$B80,원본_판매현황!$C$2:$C$500,$C80)</f>
         <v>7</v>
       </c>
-      <c r="J80" s="50" t="str">
+      <c r="J80" s="51" t="str">
         <f aca="false">'1.쇼핑검색 테스트'!I20</f>
         <v>2위</v>
       </c>
@@ -12504,7 +12646,7 @@
         <f aca="false">F46</f>
         <v>329</v>
       </c>
-      <c r="L80" s="51" t="str">
+      <c r="L80" s="52" t="str">
         <f aca="false">IF(F80&gt;D80,"광고 중 전문몰 판매 늘어남",IF(F80=0,"광고 중 전문몰 판매 없음","변화 없음"))</f>
         <v>광고 중 전문몰 판매 없음</v>
       </c>
@@ -12516,8 +12658,8 @@
       <c r="B81" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="C81" s="49" t="s">
-        <v>158</v>
+      <c r="C81" s="50" t="s">
+        <v>157</v>
       </c>
       <c r="D81" s="36" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B81,원본_판매현황!$C$2:$C$500,$C81)</f>
@@ -12527,11 +12669,11 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$57,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$57,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B81,원본_판매현황!$C$2:$C$500,$C81)</f>
         <v>5</v>
       </c>
-      <c r="F81" s="37" t="n">
+      <c r="F81" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B81,원본_판매현황!$C$2:$C$500,$C81)</f>
         <v>0</v>
       </c>
-      <c r="G81" s="37" t="n">
+      <c r="G81" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,$B81,원본_판매현황!$C$2:$C$500,$C81)</f>
         <v>0</v>
       </c>
@@ -12543,15 +12685,15 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$7,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$8,원본_판매현황!$B$2:$B$500,$B81,원본_판매현황!$C$2:$C$500,$C81)</f>
         <v>2</v>
       </c>
-      <c r="J81" s="50" t="str">
+      <c r="J81" s="51" t="str">
         <f aca="false">'1.쇼핑검색 테스트'!I21</f>
         <v>1위</v>
       </c>
       <c r="K81" s="36" t="n">
         <f aca="false">F27</f>
-        <v>96</v>
-      </c>
-      <c r="L81" s="51" t="str">
+        <v>91</v>
+      </c>
+      <c r="L81" s="52" t="str">
         <f aca="false">IF(F81&gt;D81,"광고 중 전문몰 판매 늘어남",IF(F81=0,"광고 중 전문몰 판매 없음","변화 없음"))</f>
         <v>광고 중 전문몰 판매 없음</v>
       </c>
@@ -12587,15 +12729,15 @@
         <v>234</v>
       </c>
       <c r="B86" s="3"/>
-      <c r="C86" s="40" t="n">
+      <c r="C86" s="41" t="n">
         <f aca="false">$C$9-($C$6-$C$9+1)</f>
         <v>46272</v>
       </c>
-      <c r="D86" s="40" t="n">
+      <c r="D86" s="41" t="n">
         <f aca="false">$C$9-1</f>
         <v>46286</v>
       </c>
-      <c r="E86" s="41" t="n">
+      <c r="E86" s="42" t="n">
         <f aca="false">D86-C86+1</f>
         <v>15</v>
       </c>
@@ -12605,15 +12747,15 @@
         <v>235</v>
       </c>
       <c r="B87" s="3"/>
-      <c r="C87" s="40" t="n">
+      <c r="C87" s="41" t="n">
         <f aca="false">$C$9</f>
         <v>46287</v>
       </c>
-      <c r="D87" s="40" t="n">
+      <c r="D87" s="41" t="n">
         <f aca="false">$C$6</f>
         <v>46301</v>
       </c>
-      <c r="E87" s="41" t="n">
+      <c r="E87" s="42" t="n">
         <f aca="false">D87-C87+1</f>
         <v>15</v>
       </c>
@@ -12647,7 +12789,7 @@
         <v>242</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="K89" s="10" t="s">
         <v>230</v>
@@ -12660,14 +12802,14 @@
       <c r="A90" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B90" s="52" t="s">
+      <c r="B90" s="53" t="s">
         <v>149</v>
       </c>
       <c r="C90" s="27" t="n">
         <v>2750</v>
       </c>
       <c r="D90" s="30"/>
-      <c r="E90" s="53" t="str">
+      <c r="E90" s="54" t="str">
         <f aca="false">IF(OR(C90="",D90=""),"수정 후 가격 입력 필요",D90/C90-1)</f>
         <v>수정 후 가격 입력 필요</v>
       </c>
@@ -12679,11 +12821,11 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$86,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$86,원본_판매현황!$B$2:$B$500,$A90,원본_판매현황!$C$2:$C$500,$B90)</f>
         <v>0</v>
       </c>
-      <c r="H90" s="37" t="n">
+      <c r="H90" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$9,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6,원본_판매현황!$B$2:$B$500,$A90,원본_판매현황!$C$2:$C$500,$B90)</f>
         <v>0</v>
       </c>
-      <c r="I90" s="37" t="n">
+      <c r="I90" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$9,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6,원본_판매현황!$B$2:$B$500,$A90,원본_판매현황!$C$2:$C$500,$B90)</f>
         <v>0</v>
       </c>
@@ -12691,26 +12833,26 @@
         <f aca="false">F23</f>
         <v>104</v>
       </c>
-      <c r="K90" s="51" t="str">
+      <c r="K90" s="52" t="str">
         <f aca="false">IF(H90=0,IF(F90=0,"전·후 판매 없음 · 효과 미확인","수정 후 판매 없음 · 아직 효과 없음"),IF(H90&gt;F90,"판매 늘어남",IF(H90&lt;F90,"판매 줄어듦","변화 없음")))</f>
         <v>전·후 판매 없음 · 효과 미확인</v>
       </c>
-      <c r="L90" s="54" t="s">
-        <v>151</v>
+      <c r="L90" s="55" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B91" s="52" t="s">
-        <v>166</v>
+      <c r="B91" s="53" t="s">
+        <v>164</v>
       </c>
       <c r="C91" s="27" t="n">
         <v>7700</v>
       </c>
       <c r="D91" s="30"/>
-      <c r="E91" s="53" t="str">
+      <c r="E91" s="54" t="str">
         <f aca="false">IF(OR(C91="",D91=""),"수정 후 가격 입력 필요",D91/C91-1)</f>
         <v>수정 후 가격 입력 필요</v>
       </c>
@@ -12722,11 +12864,11 @@
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$86,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$86,원본_판매현황!$B$2:$B$500,$A91,원본_판매현황!$C$2:$C$500,$B91)</f>
         <v>1</v>
       </c>
-      <c r="H91" s="37" t="n">
+      <c r="H91" s="40" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$9,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6,원본_판매현황!$B$2:$B$500,$A91,원본_판매현황!$C$2:$C$500,$B91)</f>
         <v>0</v>
       </c>
-      <c r="I91" s="37" t="n">
+      <c r="I91" s="40" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$9,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6,원본_판매현황!$B$2:$B$500,$A91,원본_판매현황!$C$2:$C$500,$B91)</f>
         <v>0</v>
       </c>
@@ -12734,12 +12876,12 @@
         <f aca="false">F32</f>
         <v>30</v>
       </c>
-      <c r="K91" s="51" t="str">
+      <c r="K91" s="52" t="str">
         <f aca="false">IF(H91=0,IF(F91=0,"전·후 판매 없음 · 효과 미확인","수정 후 판매 없음 · 아직 효과 없음"),IF(H91&gt;F91,"판매 늘어남",IF(H91&lt;F91,"판매 줄어듦","변화 없음")))</f>
         <v>수정 후 판매 없음 · 아직 효과 없음</v>
       </c>
-      <c r="L91" s="54" t="s">
-        <v>167</v>
+      <c r="L91" s="55" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12818,7 +12960,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>136</v>
@@ -12827,7 +12969,7 @@
         <v>137</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>244</v>
@@ -12844,10 +12986,10 @@
         <v>46168</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>5</v>
@@ -12870,7 +13012,7 @@
         <v>148</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>247</v>
@@ -12888,10 +13030,10 @@
         <v>46183</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>5</v>
@@ -12911,10 +13053,10 @@
         <v>46184</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>5</v>
@@ -12930,10 +13072,10 @@
         <v>46185</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>5</v>
@@ -12954,7 +13096,7 @@
         <v>148</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>5</v>
@@ -12974,10 +13116,10 @@
         <v>46195</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>5</v>
@@ -12997,10 +13139,10 @@
         <v>46203</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>5</v>
@@ -13018,10 +13160,10 @@
         <v>46211</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>251</v>
@@ -13039,10 +13181,10 @@
         <v>46234</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>251</v>
@@ -13061,7 +13203,7 @@
         <v>148</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>251</v>
@@ -13079,10 +13221,10 @@
         <v>46238</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>5</v>
@@ -13098,10 +13240,10 @@
         <v>46241</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>5</v>
@@ -13117,10 +13259,10 @@
         <v>46247</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>5</v>
@@ -13136,10 +13278,10 @@
         <v>46247</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>5</v>
@@ -13158,7 +13300,7 @@
         <v>148</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>247</v>
@@ -13176,10 +13318,10 @@
         <v>46255</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D18" s="23" t="s">
         <v>5</v>
@@ -13195,10 +13337,10 @@
         <v>46255</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>5</v>
@@ -13214,10 +13356,10 @@
         <v>46255</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>5</v>
@@ -13233,10 +13375,10 @@
         <v>46255</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>247</v>
@@ -13254,10 +13396,10 @@
         <v>46258</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>5</v>
@@ -13273,10 +13415,10 @@
         <v>46260</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>5</v>
@@ -13294,10 +13436,10 @@
         <v>46261</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>247</v>
@@ -13315,10 +13457,10 @@
         <v>46261</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>251</v>
@@ -13336,10 +13478,10 @@
         <v>46261</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>251</v>
@@ -13362,7 +13504,7 @@
         <v>148</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>251</v>
@@ -13383,7 +13525,7 @@
         <v>148</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>5</v>
@@ -13402,7 +13544,7 @@
         <v>148</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>5</v>
@@ -13437,10 +13579,10 @@
         <v>46269</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>5</v>
@@ -13456,10 +13598,10 @@
         <v>46269</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>5</v>
@@ -13478,7 +13620,7 @@
         <v>148</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>5</v>
@@ -13497,7 +13639,7 @@
         <v>148</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>5</v>
@@ -13516,7 +13658,7 @@
         <v>148</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>251</v>
@@ -13535,7 +13677,7 @@
         <v>148</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>251</v>
@@ -13551,10 +13693,10 @@
         <v>46275</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>251</v>
@@ -13573,7 +13715,7 @@
         <v>148</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>5</v>
@@ -13592,7 +13734,7 @@
         <v>148</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D39" s="23" t="s">
         <v>251</v>
@@ -13611,7 +13753,7 @@
         <v>148</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>5</v>
@@ -13627,10 +13769,10 @@
         <v>46295</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>5</v>
@@ -13646,10 +13788,10 @@
         <v>46295</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>5</v>
@@ -13665,10 +13807,10 @@
         <v>46295</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>247</v>
@@ -13687,7 +13829,7 @@
         <v>148</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D44" s="23" t="s">
         <v>5</v>
@@ -13706,7 +13848,7 @@
         <v>148</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D45" s="23" t="s">
         <v>251</v>
@@ -13722,10 +13864,10 @@
         <v>46297</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D46" s="23" t="s">
         <v>5</v>
@@ -13744,7 +13886,7 @@
         <v>148</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>251</v>
@@ -13763,7 +13905,7 @@
         <v>148</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>251</v>
@@ -13779,10 +13921,10 @@
         <v>46301</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>251</v>
@@ -13798,10 +13940,10 @@
         <v>46301</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>256</v>
@@ -13813,7 +13955,7 @@
       <c r="G50" s="23"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="55" t="s">
+      <c r="A52" s="56" t="s">
         <v>257</v>
       </c>
     </row>

--- a/보고서_쇼핑검색테스트_중국라벨판매현황.xlsx
+++ b/보고서_쇼핑검색테스트_중국라벨판매현황.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="257">
   <si>
     <t xml:space="preserve">쇼핑검색 광고 입찰가 테스트 현황</t>
   </si>
@@ -5574,7 +5574,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">판매현황의 “아트지 </t>
+      <t xml:space="preserve">판매현황의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/3 “</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아트지 </t>
     </r>
     <r>
       <rPr>
@@ -5593,64 +5612,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9/3, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문몰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">롤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 없는 규격이라 어느 규격에도 들어가지 않았습니다</t>
+      <t xml:space="preserve">건은 입력 실수라 아트지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80*60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF5A6270"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 고쳤습니다</t>
     </r>
     <r>
       <rPr>
@@ -7266,9 +7247,6 @@
       </rPr>
       <t xml:space="preserve">롤</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">80*40</t>
   </si>
   <si>
     <t xml:space="preserve">코스모스몰</t>
@@ -11081,7 +11059,7 @@
       </c>
       <c r="E29" s="36" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A29,원본_판매현황!$C$2:$C$500,$B29,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="37" t="n">
         <v>13</v>
@@ -11103,7 +11081,7 @@
       </c>
       <c r="K29" s="36" t="n">
         <f aca="false">D29-E29</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L29" s="23" t="s">
         <v>150</v>
@@ -11903,7 +11881,7 @@
       </c>
       <c r="E50" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A50,$E$23:$E$46)</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F50" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A50,$F$23:$F$46)</f>
@@ -12014,7 +11992,7 @@
       </c>
       <c r="E53" s="40" t="n">
         <f aca="false">SUM(E50:E52)</f>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F53" s="40" t="n">
         <f aca="false">SUM(F50:F52)</f>
@@ -13563,7 +13541,7 @@
         <v>148</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>5</v>
@@ -13946,7 +13924,7 @@
         <v>164</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>6</v>
@@ -13956,7 +13934,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/보고서_쇼핑검색테스트_중국라벨판매현황.xlsx
+++ b/보고서_쇼핑검색테스트_중국라벨판매현황.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="257">
   <si>
     <t xml:space="preserve">쇼핑검색 광고 입찰가 테스트 현황</t>
   </si>
@@ -5612,26 +5612,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">건은 입력 실수라 아트지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">80*60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF5A6270"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">으로 고쳤습니다</t>
+      <t xml:space="preserve">건은 중국라벨이 아니라서 기록에서 지웠습니다</t>
     </r>
     <r>
       <rPr>
@@ -7345,7 +7326,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">49</t>
+      <t xml:space="preserve">48</t>
     </r>
     <r>
       <rPr>
@@ -10648,7 +10629,7 @@
       <c r="D14" s="33"/>
       <c r="E14" s="22" t="str">
         <f aca="false">"광고 전 같은 기간 "&amp;C62&amp;"건 · "&amp;D62&amp;"롤 / 평소 수준 "&amp;TEXT(I62,"0.0")&amp;"건 · "&amp;TEXT(J62,"0.0")&amp;"롤"</f>
-        <v>광고 전 같은 기간 1건 · 5롤 / 평소 수준 2.8건 · 6.4롤</v>
+        <v>광고 전 같은 기간 1건 · 5롤 / 평소 수준 2.6건 · 6.2롤</v>
       </c>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
@@ -11059,7 +11040,7 @@
       </c>
       <c r="E29" s="36" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$B$2:$B$500,$A29,원본_판매현황!$C$2:$C$500,$B29,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$C$6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" s="37" t="n">
         <v>13</v>
@@ -11081,7 +11062,7 @@
       </c>
       <c r="K29" s="36" t="n">
         <f aca="false">D29-E29</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L29" s="23" t="s">
         <v>150</v>
@@ -11881,7 +11862,7 @@
       </c>
       <c r="E50" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A50,$E$23:$E$46)</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F50" s="36" t="n">
         <f aca="false">SUMIF($A$23:$A$46,$A50,$F$23:$F$46)</f>
@@ -11992,7 +11973,7 @@
       </c>
       <c r="E53" s="40" t="n">
         <f aca="false">SUM(E50:E52)</f>
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F53" s="40" t="n">
         <f aca="false">SUM(F50:F52)</f>
@@ -12152,19 +12133,19 @@
       </c>
       <c r="I62" s="39" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"전문몰")/$E$59*$E$58</f>
-        <v>2.79310344827586</v>
+        <v>2.63793103448276</v>
       </c>
       <c r="J62" s="39" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"전문몰")/$E$59*$E$58</f>
-        <v>6.36206896551724</v>
+        <v>6.20689655172414</v>
       </c>
       <c r="K62" s="44" t="n">
         <f aca="false">IF(I62=0,"-",E62/I62-1)</f>
-        <v>0.432098765432099</v>
+        <v>0.516339869281046</v>
       </c>
       <c r="L62" s="44" t="n">
         <f aca="false">IF(J62=0,"-",F62/J62-1)</f>
-        <v>0.257452574525745</v>
+        <v>0.288888888888889</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12244,19 +12225,19 @@
       </c>
       <c r="I64" s="39" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59)/$E$59*$E$58</f>
-        <v>4.5</v>
+        <v>4.3448275862069</v>
       </c>
       <c r="J64" s="39" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59)/$E$59*$E$58</f>
-        <v>14.1206896551724</v>
+        <v>13.9655172413793</v>
       </c>
       <c r="K64" s="44" t="n">
         <f aca="false">IF(I64=0,"-",E64/I64-1)</f>
-        <v>1.22222222222222</v>
+        <v>1.3015873015873</v>
       </c>
       <c r="L64" s="44" t="n">
         <f aca="false">IF(J64=0,"-",F64/J64-1)</f>
-        <v>1.76190476190476</v>
+        <v>1.79259259259259</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12290,19 +12271,19 @@
       </c>
       <c r="I65" s="39" t="n">
         <f aca="false">COUNTIFS(원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"아트지")/$E$59*$E$58</f>
-        <v>1.08620689655172</v>
+        <v>0.931034482758621</v>
       </c>
       <c r="J65" s="39" t="n">
         <f aca="false">SUMIFS(원본_판매현황!$E$2:$E$500,원본_판매현황!$A$2:$A$500,"&gt;="&amp;$C$59,원본_판매현황!$A$2:$A$500,"&lt;="&amp;$D$59,원본_판매현황!$D$2:$D$500,"전문몰",원본_판매현황!$B$2:$B$500,"아트지")/$E$59*$E$58</f>
-        <v>2.48275862068966</v>
+        <v>2.32758620689655</v>
       </c>
       <c r="K65" s="44" t="n">
         <f aca="false">IF(I65=0,"-",E65/I65-1)</f>
-        <v>-0.0793650793650794</v>
+        <v>0.0740740740740742</v>
       </c>
       <c r="L65" s="44" t="n">
         <f aca="false">IF(J65=0,"-",F65/J65-1)</f>
-        <v>-0.597222222222222</v>
+        <v>-0.57037037037037</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12925,7 +12906,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -13535,19 +13516,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>5</v>
       </c>
       <c r="E30" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="27"/>
       <c r="G30" s="23"/>
@@ -13560,26 +13541,26 @@
         <v>166</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>5</v>
       </c>
       <c r="E31" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="23"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>5</v>
@@ -13598,13 +13579,13 @@
         <v>148</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>5</v>
       </c>
       <c r="E33" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="27"/>
       <c r="G33" s="23"/>
@@ -13617,20 +13598,20 @@
         <v>148</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E34" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="27"/>
       <c r="G34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>148</v>
@@ -13649,13 +13630,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>251</v>
@@ -13671,13 +13652,13 @@
         <v>46275</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>251</v>
+        <v>5</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1</v>
@@ -13687,16 +13668,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="26" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>148</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E38" s="27" t="n">
         <v>1</v>
@@ -13706,7 +13687,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B39" s="23" t="s">
         <v>148</v>
@@ -13715,23 +13696,23 @@
         <v>157</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>251</v>
+        <v>5</v>
       </c>
       <c r="E39" s="27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F39" s="27"/>
       <c r="G39" s="23"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="n">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>5</v>
@@ -13750,13 +13731,13 @@
         <v>166</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>5</v>
       </c>
       <c r="E41" s="27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F41" s="27"/>
       <c r="G41" s="23"/>
@@ -13766,13 +13747,13 @@
         <v>46295</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>5</v>
+        <v>247</v>
       </c>
       <c r="E42" s="27" t="n">
         <v>1</v>
@@ -13785,13 +13766,13 @@
         <v>46295</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>247</v>
+        <v>5</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1</v>
@@ -13801,54 +13782,54 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>148</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E44" s="27" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F44" s="27"/>
       <c r="G44" s="23"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>251</v>
+        <v>5</v>
       </c>
       <c r="E45" s="27" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F45" s="27"/>
       <c r="G45" s="23"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E46" s="27" t="n">
         <v>1</v>
@@ -13880,16 +13861,16 @@
         <v>46301</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>251</v>
       </c>
       <c r="E48" s="27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F48" s="27"/>
       <c r="G48" s="23"/>
@@ -13902,38 +13883,19 @@
         <v>182</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E49" s="27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F49" s="27"/>
       <c r="G49" s="23"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="26" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="E50" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="F50" s="27"/>
-      <c r="G50" s="23"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="56" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="56" t="s">
         <v>256</v>
       </c>
     </row>
